--- a/Report/ReportUp.xlsx
+++ b/Report/ReportUp.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ppham\Documents\Do an\Report\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BACA9261-CCB7-463A-A264-DD00D509956C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E71AABBC-C440-4DEA-B688-40B1F0C1AF90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{5DBF53EA-8890-4A1E-8BE3-A300EB439DD0}"/>
   </bookViews>
@@ -593,14 +593,15 @@
   <cols>
     <col min="2" max="2" width="19.6640625" customWidth="1"/>
     <col min="3" max="3" width="12.88671875" customWidth="1"/>
-    <col min="4" max="4" width="15.77734375" customWidth="1"/>
+    <col min="4" max="4" width="15.21875" customWidth="1"/>
     <col min="5" max="5" width="9.44140625" customWidth="1"/>
     <col min="6" max="6" width="21.88671875" style="7" customWidth="1"/>
-    <col min="7" max="7" width="16.5546875" style="7" customWidth="1"/>
+    <col min="7" max="7" width="14" style="7" customWidth="1"/>
     <col min="8" max="8" width="19.77734375" style="1" customWidth="1"/>
-    <col min="9" max="9" width="31.33203125" customWidth="1"/>
-    <col min="10" max="10" width="13.33203125" customWidth="1"/>
-    <col min="11" max="11" width="15.6640625" customWidth="1"/>
+    <col min="9" max="9" width="31.6640625" customWidth="1"/>
+    <col min="10" max="10" width="12.5546875" customWidth="1"/>
+    <col min="11" max="11" width="14.33203125" customWidth="1"/>
+    <col min="12" max="12" width="12.5546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:12" s="10" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
